--- a/e2e/fixtures/file-types/report.xlsx
+++ b/e2e/fixtures/file-types/report.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1-Q4 Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Ops" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,6 +29,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -38,7 +41,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDDDDD"/>
+        <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,8 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -131,6 +137,364 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Quarterly Operations</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Q1-Q4 Summary'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Q1-Q4 Summary'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Q1-Q4 Summary'!$B$2:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Q1-Q4 Summary'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Q1-Q4 Summary'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Q1-Q4 Summary'!$C$2:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Q1-Q4 Summary'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Q1-Q4 Summary'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Q1-Q4 Summary'!$D$2:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Q1-Q4 Summary'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Q1-Q4 Summary'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Q1-Q4 Summary'!$E$2:$E$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Quarter</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Operations</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>30-day Read/Write Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Daily Ops'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Daily Ops'!$A$2:$A$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Daily Ops'!$B$2:$B$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Daily Ops'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Daily Ops'!$A$2:$A$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Daily Ops'!$C$2:$C$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -422,10 +786,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,6 +829,11 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>YoY %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,92 +842,817 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>12500</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>14800</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>17200</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
-      </c>
-      <c r="F2" t="n">
-        <v>62</v>
-      </c>
-      <c r="G2">
-        <f>SUM(B2:E2)</f>
+        <v>19400</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>+18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="F3">
+        <f>SUM(B3:E3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11200</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12800</v>
+      </c>
+      <c r="F4">
+        <f>SUM(B4:E4)</f>
+        <v/>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>+22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Replica</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F5">
+        <f>SUM(B5:E5)</f>
+        <v/>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>+34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6700</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8900</v>
+      </c>
+      <c r="F6">
+        <f>SUM(B6:E6)</f>
+        <v/>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>+12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Thumbs</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F7">
+        <f>SUM(B7:E7)</f>
+        <v/>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>+28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F8">
+        <f>SUM(B8:E8)</f>
+        <v/>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>+9%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Storage Name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>File Count</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Total Size (MB)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12480</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24800</v>
+      </c>
+      <c r="E2">
+        <f>D3/271600*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>6</v>
+          <t>s3-prod</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>9120</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>38</v>
+        <v>156400</v>
+      </c>
+      <c r="E3">
+        <f>D4/271600*100</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Replica</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+          <t>s3-backup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4560</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="n">
-        <v>26</v>
+        <v>78200</v>
+      </c>
+      <c r="E4">
+        <f>D5/271600*100</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sync</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
+          <t>sftp-archive</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sftp</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>440</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>26</v>
+        <v>12200</v>
+      </c>
+      <c r="E5">
+        <f>D6/271600*100</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Reads</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Writes</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1127</v>
+      </c>
+      <c r="C2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1179</v>
+      </c>
+      <c r="C3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>914</v>
+      </c>
+      <c r="C4" t="n">
+        <v>77</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>852</v>
+      </c>
+      <c r="C5" t="n">
+        <v>129</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C6" t="n">
+        <v>114</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>815</v>
+      </c>
+      <c r="C7" t="n">
+        <v>71</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>919</v>
+      </c>
+      <c r="C8" t="n">
+        <v>124</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>813</v>
+      </c>
+      <c r="C9" t="n">
+        <v>131</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1166</v>
+      </c>
+      <c r="C10" t="n">
+        <v>129</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>912</v>
+      </c>
+      <c r="C11" t="n">
+        <v>117</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>942</v>
+      </c>
+      <c r="C12" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1157</v>
+      </c>
+      <c r="C13" t="n">
+        <v>114</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>942</v>
+      </c>
+      <c r="C14" t="n">
+        <v>79</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C15" t="n">
+        <v>103</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>847</v>
+      </c>
+      <c r="C16" t="n">
+        <v>108</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>983</v>
+      </c>
+      <c r="C17" t="n">
+        <v>104</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>935</v>
+      </c>
+      <c r="C18" t="n">
+        <v>65</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1035</v>
+      </c>
+      <c r="C19" t="n">
+        <v>128</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>993</v>
+      </c>
+      <c r="C20" t="n">
+        <v>70</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>950</v>
+      </c>
+      <c r="C21" t="n">
+        <v>140</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>985</v>
+      </c>
+      <c r="C22" t="n">
+        <v>133</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1160</v>
+      </c>
+      <c r="C23" t="n">
+        <v>68</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1138</v>
+      </c>
+      <c r="C24" t="n">
+        <v>89</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>840</v>
+      </c>
+      <c r="C25" t="n">
+        <v>89</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>994</v>
+      </c>
+      <c r="C26" t="n">
+        <v>95</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C27" t="n">
+        <v>106</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>989</v>
+      </c>
+      <c r="C28" t="n">
+        <v>105</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1143</v>
+      </c>
+      <c r="C29" t="n">
+        <v>94</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1149</v>
+      </c>
+      <c r="C30" t="n">
+        <v>69</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C31" t="n">
+        <v>81</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>